--- a/data/trans_camb/P16-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P16-Edad-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,8; 12,78</t>
+          <t>2,6; 13,42</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,76; 7,89</t>
+          <t>-3,04; 7,78</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,96; 14,0</t>
+          <t>-2,45; 14,6</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,8; 17,17</t>
+          <t>3,75; 16,85</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-1,38; 11,43</t>
+          <t>-1,57; 11,36</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-8,2; 8,29</t>
+          <t>-8,31; 8,66</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,85; 13,66</t>
+          <t>4,46; 13,37</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-1,1; 8,0</t>
+          <t>-0,44; 8,31</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-4,38; 7,67</t>
+          <t>-3,6; 7,89</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>7,85; 72,63</t>
+          <t>11,1; 75,47</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-12,29; 44,12</t>
+          <t>-13,48; 45,23</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-14,53; 76,74</t>
+          <t>-11,33; 84,03</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8,54; 49,35</t>
+          <t>8,89; 48,63</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-3,6; 32,05</t>
+          <t>-3,74; 32,19</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-20,75; 23,44</t>
+          <t>-20,43; 23,87</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>15,49; 50,64</t>
+          <t>15,18; 50,92</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-3,74; 29,16</t>
+          <t>-1,46; 31,05</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-14,56; 28,04</t>
+          <t>-12,57; 29,06</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>8,16; 17,14</t>
+          <t>8,01; 17,87</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7,54; 17,04</t>
+          <t>7,63; 17,41</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7,09; 20,72</t>
+          <t>7,03; 20,65</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8,79; 20,64</t>
+          <t>9,17; 20,21</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,66; 9,89</t>
+          <t>-2,11; 9,81</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,54; 26,88</t>
+          <t>0,21; 31,07</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10,27; 17,92</t>
+          <t>9,77; 17,35</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>5,12; 12,82</t>
+          <t>5,16; 12,76</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>7,35; 26,79</t>
+          <t>7,48; 27,57</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>35,63; 92,08</t>
+          <t>35,12; 97,26</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>31,86; 92,51</t>
+          <t>33,49; 96,17</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>31,13; 109,69</t>
+          <t>33,06; 113,75</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>18,84; 50,88</t>
+          <t>19,38; 49,22</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-3,63; 24,25</t>
+          <t>-4,87; 23,58</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-1,32; 63,41</t>
+          <t>0,21; 74,61</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>31,49; 62,2</t>
+          <t>29,29; 58,68</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>15,62; 44,77</t>
+          <t>15,75; 43,88</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>22,97; 91,31</t>
+          <t>23,41; 90,24</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>4,4; 15,34</t>
+          <t>4,79; 15,73</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4,04; 14,59</t>
+          <t>3,88; 14,43</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6,47; 17,6</t>
+          <t>6,31; 17,24</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10,38; 21,34</t>
+          <t>10,01; 21,34</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,85; 12,1</t>
+          <t>1,35; 11,53</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-0,19; 10,65</t>
+          <t>-0,53; 9,83</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,74; 16,45</t>
+          <t>8,76; 16,13</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>3,55; 11,61</t>
+          <t>3,52; 11,33</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>4,09; 12,27</t>
+          <t>4,2; 12,19</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>15,32; 61,28</t>
+          <t>16,13; 63,63</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>13,66; 60,16</t>
+          <t>13,6; 58,66</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>21,27; 70,65</t>
+          <t>21,34; 69,12</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>21,22; 50,21</t>
+          <t>20,49; 49,89</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1,76; 28,83</t>
+          <t>2,32; 26,87</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-0,36; 25,51</t>
+          <t>-1,13; 23,41</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>22,57; 46,97</t>
+          <t>22,57; 46,25</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>9,49; 33,46</t>
+          <t>9,16; 32,71</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>10,57; 35,8</t>
+          <t>10,67; 34,84</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,53; 13,37</t>
+          <t>1,11; 14,02</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>5,62; 17,83</t>
+          <t>5,63; 18,08</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-26,62; 13,24</t>
+          <t>-25,68; 12,91</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6,8; 18,62</t>
+          <t>6,56; 18,77</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,73; 10,48</t>
+          <t>-1,59; 10,24</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-6,87; 7,97</t>
+          <t>-8,26; 8,16</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,84; 14,58</t>
+          <t>5,82; 14,79</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>4,16; 12,56</t>
+          <t>4,04; 12,31</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-21,89; 8,41</t>
+          <t>-21,36; 8,58</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>3,35; 35,52</t>
+          <t>2,71; 38,43</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>12,7; 48,93</t>
+          <t>13,41; 49,66</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-59,83; 34,5</t>
+          <t>-59,91; 33,28</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>11,07; 35,01</t>
+          <t>10,77; 34,87</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-2,8; 19,76</t>
+          <t>-2,7; 19,5</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-11,46; 14,72</t>
+          <t>-13,98; 15,22</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>11,64; 31,96</t>
+          <t>11,48; 32,29</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>8,38; 27,38</t>
+          <t>7,82; 26,53</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-44,8; 17,71</t>
+          <t>-40,71; 17,84</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-3,67; 8,45</t>
+          <t>-3,8; 8,75</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-13,94; -1,3</t>
+          <t>-14,24; -1,27</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-7,79; 3,9</t>
+          <t>-8,63; 3,35</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2,13; 13,3</t>
+          <t>1,74; 13,57</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-1,02; 10,24</t>
+          <t>-1,84; 10,11</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-4,57; 5,79</t>
+          <t>-4,77; 5,3</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,18; 9,64</t>
+          <t>1,17; 9,36</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-5,7; 2,81</t>
+          <t>-5,94; 3,3</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-4,71; 3,05</t>
+          <t>-4,68; 2,5</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-4,82; 12,18</t>
+          <t>-5,11; 12,64</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-18,41; -1,93</t>
+          <t>-19,19; -1,86</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-10,28; 5,51</t>
+          <t>-11,43; 4,82</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2,93; 18,93</t>
+          <t>2,52; 19,06</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-1,27; 14,43</t>
+          <t>-2,49; 14,16</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-5,86; 7,99</t>
+          <t>-6,01; 7,47</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>1,53; 13,47</t>
+          <t>1,52; 13,15</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-7,51; 3,89</t>
+          <t>-7,71; 4,66</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-6,21; 4,25</t>
+          <t>-6,12; 3,51</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>3,69; 15,52</t>
+          <t>3,41; 15,54</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-1,55; 11,62</t>
+          <t>-1,09; 11,64</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-7,62; 4,05</t>
+          <t>-8,06; 3,16</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-2,56; 5,64</t>
+          <t>-2,79; 5,86</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-2,26; 5,86</t>
+          <t>-2,85; 5,7</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-8,31; 7,47</t>
+          <t>-8,17; 7,51</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,49; 8,88</t>
+          <t>1,77; 9,03</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-0,87; 6,67</t>
+          <t>-0,61; 6,59</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-6,33; 7,49</t>
+          <t>-6,1; 7,09</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>4,44; 20,54</t>
+          <t>4,25; 21,15</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-1,92; 15,34</t>
+          <t>-1,38; 15,4</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-9,32; 5,23</t>
+          <t>-9,66; 4,16</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-2,76; 6,36</t>
+          <t>-3,01; 6,65</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-2,49; 6,6</t>
+          <t>-3,09; 6,7</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-9,2; 8,8</t>
+          <t>-9,04; 8,63</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>1,72; 10,72</t>
+          <t>2,04; 10,87</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-1,02; 8,01</t>
+          <t>-0,73; 7,88</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-7,31; 9,01</t>
+          <t>-7,13; 8,65</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-0,61; 9,68</t>
+          <t>-1,26; 9,39</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-3,27; 7,07</t>
+          <t>-3,86; 6,71</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-8,42; 2,24</t>
+          <t>-8,22; 2,5</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>0,3; 6,92</t>
+          <t>0,49; 7,57</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-1,77; 6,01</t>
+          <t>-1,74; 5,87</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-4,85; 2,08</t>
+          <t>-4,78; 2,13</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>0,87; 6,59</t>
+          <t>0,91; 6,74</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-1,16; 4,83</t>
+          <t>-1,27; 4,94</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-4,87; 0,97</t>
+          <t>-5,25; 0,82</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 11,28</t>
+          <t>-1,36; 10,94</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-3,59; 8,11</t>
+          <t>-4,2; 7,73</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-9,17; 2,58</t>
+          <t>-8,9; 2,93</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>0,32; 7,7</t>
+          <t>0,53; 8,43</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-1,87; 6,59</t>
+          <t>-1,82; 6,47</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-5,07; 2,3</t>
+          <t>-4,97; 2,35</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>0,93; 7,3</t>
+          <t>1,04; 7,64</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-1,29; 5,38</t>
+          <t>-1,36; 5,48</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-5,23; 1,08</t>
+          <t>-5,57; 0,91</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>7,44; 12,38</t>
+          <t>7,47; 12,47</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>6,94; 11,68</t>
+          <t>6,78; 11,73</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-2,69; 13,28</t>
+          <t>-2,13; 13,64</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>9,24; 14,02</t>
+          <t>9,3; 14,03</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>3,73; 8,51</t>
+          <t>3,73; 8,57</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>4,37; 14,35</t>
+          <t>4,11; 13,91</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>9,09; 12,56</t>
+          <t>9,18; 12,61</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>6,16; 9,49</t>
+          <t>6,03; 9,32</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>1,57; 11,91</t>
+          <t>1,74; 11,9</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>17,8; 31,66</t>
+          <t>18,09; 32,01</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>16,35; 29,76</t>
+          <t>16,38; 30,12</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-6,28; 32,95</t>
+          <t>-5,12; 34,21</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>15,46; 24,38</t>
+          <t>15,6; 24,48</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>6,26; 14,95</t>
+          <t>6,23; 15,09</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>7,37; 24,58</t>
+          <t>6,87; 24,0</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>18,04; 25,76</t>
+          <t>18,0; 25,78</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>12,2; 19,39</t>
+          <t>12,01; 19,11</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>3,19; 24,2</t>
+          <t>3,46; 24,17</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P16-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P16-Edad-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5,1</t>
+          <t>5,26</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-0,52</t>
+          <t>0,57</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>1,78</t>
+          <t>2,77</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,6; 13,42</t>
+          <t>2,01; 13,2</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,04; 7,78</t>
+          <t>-3,38; 7,57</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,45; 14,6</t>
+          <t>-2,48; 12,71</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,75; 16,85</t>
+          <t>4,09; 17,3</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-1,57; 11,36</t>
+          <t>-0,78; 11,85</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-8,31; 8,66</t>
+          <t>-7,29; 9,04</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,46; 13,37</t>
+          <t>5,25; 13,8</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-0,44; 8,31</t>
+          <t>-0,26; 8,01</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-3,6; 7,89</t>
+          <t>-2,64; 8,78</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>25,65%</t>
+          <t>26,46%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-1,36%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>9,65%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>11,1; 75,47</t>
+          <t>9,62; 76,14</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-13,48; 45,23</t>
+          <t>-15,23; 43,03</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-11,33; 84,03</t>
+          <t>-11,66; 70,03</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8,89; 48,63</t>
+          <t>9,78; 50,34</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-3,74; 32,19</t>
+          <t>-1,75; 34,4</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-20,43; 23,87</t>
+          <t>-18,15; 24,15</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>15,18; 50,92</t>
+          <t>17,22; 50,93</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-1,46; 31,05</t>
+          <t>-0,88; 30,32</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-12,57; 29,06</t>
+          <t>-8,49; 32,5</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>13,84</t>
+          <t>12,74</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>9,51</t>
+          <t>0,1</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>13,53</t>
+          <t>7,51</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>8,01; 17,87</t>
+          <t>8,13; 17,24</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7,63; 17,41</t>
+          <t>7,15; 17,15</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7,03; 20,65</t>
+          <t>6,64; 19,32</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>9,17; 20,21</t>
+          <t>9,54; 21,3</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-2,11; 9,81</t>
+          <t>-1,98; 9,76</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,21; 31,07</t>
+          <t>-6,1; 6,38</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9,77; 17,35</t>
+          <t>9,83; 17,36</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>5,16; 12,76</t>
+          <t>4,99; 12,8</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>7,48; 27,57</t>
+          <t>2,47; 12,04</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>68,96%</t>
+          <t>63,48%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>21,77%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>43,77%</t>
+          <t>24,29%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>35,12; 97,26</t>
+          <t>36,3; 96,07</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>33,49; 96,17</t>
+          <t>31,87; 94,69</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>33,06; 113,75</t>
+          <t>27,87; 102,07</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>19,38; 49,22</t>
+          <t>20,38; 53,43</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-4,87; 23,58</t>
+          <t>-4,27; 23,22</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,21; 74,61</t>
+          <t>-13,14; 15,79</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>29,29; 58,68</t>
+          <t>30,11; 59,19</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>15,75; 43,88</t>
+          <t>15,51; 43,57</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>23,41; 90,24</t>
+          <t>7,92; 41,35</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>11,81</t>
+          <t>10,11</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5,06</t>
+          <t>4,6</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>8,12</t>
+          <t>7,01</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>4,79; 15,73</t>
+          <t>4,42; 14,9</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,88; 14,43</t>
+          <t>3,54; 14,38</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6,31; 17,24</t>
+          <t>4,59; 15,27</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10,01; 21,34</t>
+          <t>10,26; 20,45</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,35; 11,53</t>
+          <t>0,85; 11,73</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-0,53; 9,83</t>
+          <t>-0,1; 9,99</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,76; 16,13</t>
+          <t>8,82; 16,28</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>3,52; 11,33</t>
+          <t>3,43; 10,9</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>4,2; 12,19</t>
+          <t>3,07; 10,88</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>43,09%</t>
+          <t>36,89%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>10,17%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>22,13%</t>
+          <t>19,12%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>16,13; 63,63</t>
+          <t>14,77; 60,84</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>13,6; 58,66</t>
+          <t>11,87; 58,77</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>21,34; 69,12</t>
+          <t>16,17; 61,82</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>20,49; 49,89</t>
+          <t>21,78; 48,91</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2,32; 26,87</t>
+          <t>1,9; 27,99</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-1,13; 23,41</t>
+          <t>-0,28; 23,82</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>22,57; 46,25</t>
+          <t>22,39; 47,3</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>9,16; 32,71</t>
+          <t>8,91; 31,32</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>10,67; 34,84</t>
+          <t>7,91; 30,88</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-2,88</t>
+          <t>10,59</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,26</t>
+          <t>4,28</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-1,49</t>
+          <t>7,6</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,11; 14,02</t>
+          <t>1,36; 13,73</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>5,63; 18,08</t>
+          <t>5,89; 17,85</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-25,68; 12,91</t>
+          <t>4,82; 16,75</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6,56; 18,77</t>
+          <t>6,66; 18,1</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,59; 10,24</t>
+          <t>-1,59; 10,11</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-8,26; 8,16</t>
+          <t>0,16; 10,36</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,82; 14,79</t>
+          <t>5,84; 14,71</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>4,04; 12,31</t>
+          <t>4,13; 12,53</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-21,36; 8,58</t>
+          <t>3,88; 11,81</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-7,25%</t>
+          <t>26,64%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-3,09%</t>
+          <t>15,77%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>2,71; 38,43</t>
+          <t>3,44; 38,1</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>13,41; 49,66</t>
+          <t>13,45; 47,29</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-59,91; 33,28</t>
+          <t>11,3; 46,25</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>10,77; 34,87</t>
+          <t>11,28; 34,05</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-2,7; 19,5</t>
+          <t>-2,45; 18,78</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-13,98; 15,22</t>
+          <t>0,36; 19,84</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>11,48; 32,29</t>
+          <t>11,74; 32,19</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>7,82; 26,53</t>
+          <t>8,3; 27,3</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-40,71; 17,84</t>
+          <t>7,77; 26,12</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-2,09</t>
+          <t>-3,57</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,14</t>
+          <t>-0,03</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-1,03</t>
+          <t>-1,83</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-3,8; 8,75</t>
+          <t>-4,05; 8,6</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-14,24; -1,27</t>
+          <t>-13,78; -1,55</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-8,63; 3,35</t>
+          <t>-9,07; 2,46</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1,74; 13,57</t>
+          <t>1,82; 13,86</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-1,84; 10,11</t>
+          <t>-1,28; 9,95</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-4,77; 5,3</t>
+          <t>-4,63; 5,16</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,17; 9,36</t>
+          <t>1,03; 9,49</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-5,94; 3,3</t>
+          <t>-6,38; 2,56</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-4,68; 2,5</t>
+          <t>-5,92; 1,92</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-2,86%</t>
+          <t>-4,9%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>-0,03%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-1,39%</t>
+          <t>-2,47%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-5,11; 12,64</t>
+          <t>-5,41; 12,37</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-19,19; -1,86</t>
+          <t>-18,27; -2,22</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-11,43; 4,82</t>
+          <t>-12,12; 3,4</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2,52; 19,06</t>
+          <t>2,33; 19,56</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-2,49; 14,16</t>
+          <t>-1,6; 13,95</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-6,01; 7,47</t>
+          <t>-5,92; 7,27</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>1,52; 13,15</t>
+          <t>1,37; 13,43</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-7,71; 4,66</t>
+          <t>-8,41; 3,54</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-6,12; 3,51</t>
+          <t>-7,66; 2,67</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>-2,29</t>
+          <t>-2,68</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>-1,38</t>
+          <t>-6,89</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>-0,79</t>
+          <t>-5,09</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>3,41; 15,54</t>
+          <t>3,77; 15,38</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-1,09; 11,64</t>
+          <t>-1,35; 10,84</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-8,06; 3,16</t>
+          <t>-8,59; 2,86</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-2,79; 5,86</t>
+          <t>-2,56; 5,98</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-2,85; 5,7</t>
+          <t>-2,8; 5,38</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-8,17; 7,51</t>
+          <t>-10,85; -2,75</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,77; 9,03</t>
+          <t>1,1; 8,62</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-0,61; 6,59</t>
+          <t>-0,74; 6,45</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-6,1; 7,09</t>
+          <t>-8,65; -1,53</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>-2,89%</t>
+          <t>-3,38%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>-1,52%</t>
+          <t>-7,64%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>-0,93%</t>
+          <t>-5,99%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>4,25; 21,15</t>
+          <t>4,49; 20,77</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-1,38; 15,4</t>
+          <t>-1,7; 14,45</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-9,66; 4,16</t>
+          <t>-10,44; 3,71</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-3,01; 6,65</t>
+          <t>-2,79; 6,83</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-3,09; 6,7</t>
+          <t>-2,99; 6,13</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-9,04; 8,63</t>
+          <t>-11,91; -3,18</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>2,04; 10,87</t>
+          <t>1,27; 10,26</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-0,73; 7,88</t>
+          <t>-0,88; 7,75</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-7,13; 8,65</t>
+          <t>-9,97; -1,83</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>-2,99</t>
+          <t>-3,23</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>-1,58</t>
+          <t>-1,89</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>-2,2</t>
+          <t>-2,49</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-1,26; 9,39</t>
+          <t>-0,99; 9,15</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-3,86; 6,71</t>
+          <t>-3,54; 6,92</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-8,22; 2,5</t>
+          <t>-8,81; 1,97</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>0,49; 7,57</t>
+          <t>0,34; 7,29</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-1,74; 5,87</t>
+          <t>-1,86; 5,78</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-4,78; 2,13</t>
+          <t>-5,5; 1,66</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>0,91; 6,74</t>
+          <t>0,54; 6,78</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-1,27; 4,94</t>
+          <t>-1,29; 4,96</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-5,25; 0,82</t>
+          <t>-5,46; 0,6</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>-3,34%</t>
+          <t>-3,62%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>-1,7%</t>
+          <t>-2,02%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>-2,39%</t>
+          <t>-2,71%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-1,36; 10,94</t>
+          <t>-1,07; 10,81</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-4,2; 7,73</t>
+          <t>-3,85; 8,12</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-8,9; 2,93</t>
+          <t>-9,61; 2,28</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>0,53; 8,43</t>
+          <t>0,38; 8,12</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-1,82; 6,47</t>
+          <t>-1,96; 6,37</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-4,97; 2,35</t>
+          <t>-5,74; 1,83</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>1,04; 7,64</t>
+          <t>0,63; 7,64</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-1,36; 5,48</t>
+          <t>-1,37; 5,54</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-5,57; 0,91</t>
+          <t>-5,85; 0,65</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>8,76</t>
+          <t>11,69</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>7,65</t>
+          <t>4,76</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>8,3</t>
+          <t>8,24</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>7,47; 12,47</t>
+          <t>7,44; 12,54</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>6,78; 11,73</t>
+          <t>6,74; 11,61</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-2,13; 13,64</t>
+          <t>8,98; 14,19</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>9,3; 14,03</t>
+          <t>9,34; 13,89</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>3,73; 8,57</t>
+          <t>3,98; 8,68</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>4,11; 13,91</t>
+          <t>2,65; 6,88</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>9,18; 12,61</t>
+          <t>9,34; 12,65</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>6,03; 9,32</t>
+          <t>6,08; 9,55</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>1,74; 11,9</t>
+          <t>6,63; 10,12</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>21,61%</t>
+          <t>28,85%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>13,06%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>16,58%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>18,09; 32,01</t>
+          <t>17,97; 32,02</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>16,38; 30,12</t>
+          <t>16,15; 29,7</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-5,12; 34,21</t>
+          <t>21,57; 36,35</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>15,6; 24,48</t>
+          <t>15,5; 24,19</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>6,23; 15,09</t>
+          <t>6,57; 15,21</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>6,87; 24,0</t>
+          <t>4,48; 12,12</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>18,0; 25,78</t>
+          <t>18,55; 26,01</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>12,01; 19,11</t>
+          <t>11,98; 19,52</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>3,46; 24,17</t>
+          <t>13,19; 20,79</t>
         </is>
       </c>
     </row>
